--- a/开销记录/国网数科.xlsx
+++ b/开销记录/国网数科.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aptx4869\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aptx4869\Desktop\GWSK-CP-ABE\开销记录\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9E44B9-DBFB-4443-A365-BE0AF850705E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1141F960-5A5A-4915-B2CF-2FB876EC8E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -134,6 +134,430 @@
   </si>
   <si>
     <r>
+      <t>Setup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>KeyGen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Enc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>密钥数量</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2^8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>256</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2^9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>512</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2^10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2^11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2048</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2^12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4096</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里用柱形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里用折线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三者同一个图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Gen</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Sig</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Ver</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>RSA</t>
     </r>
     <r>
@@ -144,7 +568,8 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>密钥对</t>
+      <t>密钥对
+只运行了一次</t>
     </r>
     <r>
       <rPr>
@@ -160,13 +585,55 @@
   </si>
   <si>
     <r>
-      <t>Setup</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>签名生成、签名验证
+循环</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算能力和带宽有限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>sign_verify</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
         <family val="1"/>
         <charset val="134"/>
       </rPr>
@@ -174,8 +641,9 @@
     </r>
     <r>
       <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -183,9 +651,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
         <family val="1"/>
         <charset val="134"/>
       </rPr>
@@ -195,13 +664,14 @@
   </si>
   <si>
     <r>
-      <t>KeyGen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
+      <t>merkle_verify</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
         <family val="1"/>
         <charset val="134"/>
       </rPr>
@@ -209,8 +679,9 @@
     </r>
     <r>
       <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -218,9 +689,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
         <family val="1"/>
         <charset val="134"/>
       </rPr>
@@ -230,13 +702,14 @@
   </si>
   <si>
     <r>
-      <t>Enc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
+      <t>Ver</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
         <family val="1"/>
         <charset val="134"/>
       </rPr>
@@ -244,6 +717,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="16"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
@@ -253,10 +727,67 @@
     </r>
     <r>
       <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="1"/>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sign_verify + merkle_verify</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IRBA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BASA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Sig</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -265,13 +796,14 @@
   </si>
   <si>
     <r>
-      <t>Gen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
+      <t>Ver</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
         <family val="1"/>
         <charset val="134"/>
       </rPr>
@@ -279,6 +811,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="16"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
@@ -288,292 +821,15 @@
     </r>
     <r>
       <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
         <family val="1"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Ver</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ms</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>密钥数量</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2^8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>256</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2^9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>512</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2^10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2^11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2048</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2^12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>4096</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Sig</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ms</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里用柱形</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里用折线</t>
-  </si>
-  <si>
-    <t>这里用折线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一个图</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三者同一个图</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -581,10 +837,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.0000"/>
+    <numFmt numFmtId="178" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -694,8 +951,54 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -720,8 +1023,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -788,11 +1109,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -809,6 +1139,12 @@
     <xf numFmtId="176" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -818,19 +1154,40 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1113,42 +1470,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="20.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="62.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="20.625" style="1" customWidth="1"/>
     <col min="12" max="21" width="24.75" style="1" customWidth="1"/>
     <col min="22" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="1:7" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -1160,259 +1512,508 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>10</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="19">
         <v>2.5573350000000001</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="19">
         <v>42.859974999999999</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="19">
         <v>43.620930999999999</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="19">
         <v>11.885471000000001</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="19">
         <v>6.7905999999999994E-2</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="21" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>20</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="19">
         <v>2.6740780000000002</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="19">
         <v>76.995339999999999</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="19">
         <v>85.151117999999997</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="19">
         <v>22.811855000000001</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="19">
         <v>6.9924E-2</v>
       </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>30</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="19">
         <v>2.8359990000000002</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="19">
         <v>106.997899</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="19">
         <v>123.02942299999999</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="19">
         <v>32.390200999999998</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="19">
         <v>6.5294000000000005E-2</v>
       </c>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="22"/>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>40</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="19">
         <v>2.6853229999999999</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="19">
         <v>138.55750699999999</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="19">
         <v>161.911518</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="19">
         <v>45.437337999999997</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="19">
         <v>6.5157999999999994E-2</v>
       </c>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G6" s="22"/>
+    </row>
+    <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>50</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="19">
         <v>2.7396410000000002</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="19">
         <v>171.35196300000001</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="19">
         <v>202.050907</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="19">
         <v>53.874381999999997</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="19">
         <v>6.6238000000000005E-2</v>
       </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="G7" s="22"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B8" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="10" spans="1:11" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="J10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="1:11" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5">
         <v>66.0244</v>
       </c>
-      <c r="C12" s="5">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="D12" s="5">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="13">
+        <v>2.7</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4.3087999999999997</v>
+      </c>
+      <c r="H12" s="5">
+        <v>3.2119</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5">
         <v>131.98480000000001</v>
       </c>
-      <c r="C13" s="5">
-        <v>2.8E-3</v>
-      </c>
-      <c r="D13" s="5">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="13">
+        <v>2.8</v>
+      </c>
+      <c r="D13" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14" s="5">
         <v>277.15370000000001</v>
       </c>
-      <c r="C14" s="5">
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="D14" s="5">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="13">
+        <v>2.9</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5">
         <v>525.71910000000003</v>
       </c>
-      <c r="C15" s="5">
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="D15" s="5">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="13">
+        <v>2.9</v>
+      </c>
+      <c r="D15" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5">
         <v>1055.6633999999999</v>
       </c>
-      <c r="C16" s="5">
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="D16" s="5">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="13" t="s">
-        <v>24</v>
+      <c r="C16" s="13">
+        <v>2.9</v>
+      </c>
+      <c r="D16" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
+    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="5">
+        <v>66.740399999999994</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1.3420000000000001</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.59289999999999998</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="5">
+        <v>133.6474</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1.2630999999999999</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.56310000000000004</v>
+      </c>
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="5">
+        <v>265.58280000000002</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1.3405</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.59030000000000005</v>
+      </c>
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="5">
+        <v>532.73979999999995</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1.2676000000000001</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.56110000000000004</v>
+      </c>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="5">
+        <v>1063.7551000000001</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1.3016000000000001</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0.59379999999999999</v>
+      </c>
+      <c r="E24" s="9"/>
+    </row>
+    <row r="27" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" ht="66" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>1</v>
+      </c>
+      <c r="B29" s="20">
+        <f>66672.4801063537/1000</f>
+        <v>66.672480106353703</v>
+      </c>
+      <c r="C29" s="20">
+        <f>1.06430053710937*2</f>
+        <v>2.1286010742187398</v>
+      </c>
+      <c r="D29" s="16">
+        <f>0.271797180175781*2</f>
+        <v>0.54359436035156194</v>
+      </c>
+      <c r="E29" s="16">
+        <f>0.0162124633789062*2</f>
+        <v>3.2424926757812403E-2</v>
+      </c>
+      <c r="F29" s="20">
+        <f>(0.271797180175781+0.0162124633789062)*2</f>
+        <v>0.57601928710937433</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="B30" s="20">
+        <f>104542.313814163/1000</f>
+        <v>104.54231381416301</v>
+      </c>
+      <c r="C30" s="20">
+        <f>10.3404521942138*2</f>
+        <v>20.680904388427599</v>
+      </c>
+      <c r="D30" s="16">
+        <f>1.51419639587402*2</f>
+        <v>3.0283927917480402</v>
+      </c>
+      <c r="E30" s="16">
+        <f>1.30200386047363*2</f>
+        <v>2.6040077209472599</v>
+      </c>
+      <c r="F30" s="20">
+        <f>(1.51419639587402+1.30200386047363)*2</f>
+        <v>5.6324005126953001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="B31" s="20">
+        <f>181407.611846923/1000</f>
+        <v>181.407611846923</v>
+      </c>
+      <c r="C31" s="20">
+        <f>17.8208351135253*2</f>
+        <v>35.641670227050597</v>
+      </c>
+      <c r="D31" s="16">
+        <f>2.16889381408691*2</f>
+        <v>4.3377876281738201</v>
+      </c>
+      <c r="E31" s="16">
+        <f>2.19559669494628*2</f>
+        <v>4.3911933898925604</v>
+      </c>
+      <c r="F31" s="20">
+        <f>(2.16889381408691+2.19559669494628)*2</f>
+        <v>8.7289810180663814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="B32" s="20">
+        <f>361442.13104248/1000</f>
+        <v>361.44213104248001</v>
+      </c>
+      <c r="C32" s="20">
+        <f>35.994529724121*2</f>
+        <v>71.989059448242003</v>
+      </c>
+      <c r="D32" s="16">
+        <f>9.69624519348144*2</f>
+        <v>19.39249038696288</v>
+      </c>
+      <c r="E32" s="16">
+        <f>4.47344779968261*2</f>
+        <v>8.9468955993652202</v>
+      </c>
+      <c r="F32" s="20">
+        <f>(9.69624519348144+4.47344779968261)*2</f>
+        <v>28.3393859863281</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="E20:E24"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="G3:G7"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:F10"/>
     <mergeCell ref="E12:E16"/>
     <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="G10:H10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/开销记录/国网数科.xlsx
+++ b/开销记录/国网数科.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aptx4869\Desktop\GWSK-CP-ABE\开销记录\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1141F960-5A5A-4915-B2CF-2FB876EC8E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02CA1AC-CB47-43F2-AF23-EE6434AAFCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
   <si>
     <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -427,22 +429,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>这里用柱形</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里用折线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一个图</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三者同一个图</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>Gen</t>
     </r>
@@ -557,6 +543,652 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>利用率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>sign_verify</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>merkle_verify</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Ver</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sign_verify + merkle_verify</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IRBA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BASA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Sig</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Ver</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>签名耗时</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>验证耗时</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统吞吐量</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ops/sec</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>计算能力和带宽有限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Merkle Hash Tree</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>线程数</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>总耗时（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大内核</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>24
+1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">次任务
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>rbits=160</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>qbits=512</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>rbits=160</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>qbits=512</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大内核</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>24
+1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">次任务
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>rbits = 160</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qbits = 512
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">参与方数量 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">n = 5
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">门限 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>t = 4</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ours</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一个图</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>RSA</t>
     </r>
@@ -568,8 +1200,28 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>密钥对
-只运行了一次</t>
+      <t xml:space="preserve">密钥对
+只运行了一次
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>版本</t>
     </r>
     <r>
       <rPr>
@@ -586,6 +1238,58 @@
   <si>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这里用折线</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这里用柱形</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这里用柱形</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三者同一个图</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
@@ -614,221 +1318,95 @@
       </rPr>
       <t>次</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>利用率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算能力和带宽有限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>sign_verify</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ms</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>merkle_verify</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ms</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Ver</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ms</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）=</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>sign_verify + merkle_verify</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IRBA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BASA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Sig</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ms</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Ver</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ms</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
+      <t>版本</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大内核</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>24
+1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次任务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+112</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比特安全</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>112</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比特安全</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -839,9 +1417,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.0000"/>
-    <numFmt numFmtId="178" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -975,13 +1553,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
@@ -994,6 +1565,48 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="134"/>
     </font>
@@ -1124,9 +1737,6 @@
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1139,32 +1749,11 @@
     <xf numFmtId="176" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1175,19 +1764,41 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1470,553 +2081,1251 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="20.625" style="1" customWidth="1"/>
-    <col min="12" max="21" width="24.75" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="21.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="20.625" style="5" customWidth="1"/>
+    <col min="11" max="17" width="24.75" style="5" customWidth="1"/>
+    <col min="18" max="16384" width="8.875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-    </row>
-    <row r="2" spans="1:11" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:7" s="5" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:7" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>10</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="10">
         <v>2.5573350000000001</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="10">
         <v>42.859974999999999</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="10">
         <v>43.620930999999999</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="10">
         <v>11.885471000000001</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="10">
         <v>6.7905999999999994E-2</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row r="4" spans="1:7" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>20</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="10">
         <v>2.6740780000000002</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="10">
         <v>76.995339999999999</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="10">
         <v>85.151117999999997</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="10">
         <v>22.811855000000001</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="10">
         <v>6.9924E-2</v>
       </c>
-      <c r="G4" s="22"/>
-    </row>
-    <row r="5" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>30</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="10">
         <v>2.8359990000000002</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="10">
         <v>106.997899</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="10">
         <v>123.02942299999999</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="10">
         <v>32.390200999999998</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="10">
         <v>6.5294000000000005E-2</v>
       </c>
-      <c r="G5" s="22"/>
-    </row>
-    <row r="6" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>40</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="10">
         <v>2.6853229999999999</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="10">
         <v>138.55750699999999</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="10">
         <v>161.911518</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="10">
         <v>45.437337999999997</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="10">
         <v>6.5157999999999994E-2</v>
       </c>
-      <c r="G6" s="22"/>
-    </row>
-    <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>50</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="10">
         <v>2.7396410000000002</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="10">
         <v>171.35196300000001</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="10">
         <v>202.050907</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="10">
         <v>53.874381999999997</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="10">
         <v>6.6238000000000005E-2</v>
       </c>
-      <c r="G7" s="22"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="18" t="s">
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+    </row>
+    <row r="10" spans="1:7" s="5" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" s="5" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-    </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="J10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="10"/>
-    </row>
-    <row r="11" spans="1:11" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    </row>
+    <row r="12" spans="1:7" s="5" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>66.0244</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="6">
         <v>2.7</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="6">
         <v>0.9</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="5">
-        <v>4.3087999999999997</v>
-      </c>
-      <c r="H12" s="5">
-        <v>3.2119</v>
-      </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="E12" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>131.98480000000001</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="6">
         <v>2.8</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="6">
         <v>0.9</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="E13" s="15"/>
+    </row>
+    <row r="14" spans="1:7" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>277.15370000000001</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="6">
         <v>2.9</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="6">
         <v>0.9</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="E14" s="15"/>
+    </row>
+    <row r="15" spans="1:7" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>525.71910000000003</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="6">
         <v>2.9</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="6">
         <v>0.9</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="E15" s="15"/>
+    </row>
+    <row r="16" spans="1:7" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>1055.6633999999999</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="6">
         <v>2.9</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="6">
         <v>0.9</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B18" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="E16" s="15"/>
+    </row>
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+    </row>
+    <row r="19" spans="1:5" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:5" s="5" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>66.740399999999994</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>1.3420000000000001</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>0.59289999999999998</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="E20" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>133.6474</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>1.2630999999999999</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>0.56310000000000004</v>
       </c>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="E21" s="15"/>
+    </row>
+    <row r="22" spans="1:5" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>265.58280000000002</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>1.3405</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>0.59030000000000005</v>
       </c>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="E22" s="15"/>
+    </row>
+    <row r="23" spans="1:5" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>532.73979999999995</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <v>1.2676000000000001</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>0.56110000000000004</v>
       </c>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="E23" s="15"/>
+    </row>
+    <row r="24" spans="1:5" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>1063.7551000000001</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>1.3016000000000001</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>0.59379999999999999</v>
       </c>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="27" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-    </row>
-    <row r="28" spans="1:6" ht="66" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>1</v>
-      </c>
-      <c r="B29" s="20">
-        <f>66672.4801063537/1000</f>
-        <v>66.672480106353703</v>
-      </c>
-      <c r="C29" s="20">
-        <f>1.06430053710937*2</f>
-        <v>2.1286010742187398</v>
-      </c>
-      <c r="D29" s="16">
-        <f>0.271797180175781*2</f>
-        <v>0.54359436035156194</v>
-      </c>
-      <c r="E29" s="16">
-        <f>0.0162124633789062*2</f>
-        <v>3.2424926757812403E-2</v>
-      </c>
-      <c r="F29" s="20">
-        <f>(0.271797180175781+0.0162124633789062)*2</f>
-        <v>0.57601928710937433</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="B30" s="20">
-        <f>104542.313814163/1000</f>
-        <v>104.54231381416301</v>
-      </c>
-      <c r="C30" s="20">
-        <f>10.3404521942138*2</f>
-        <v>20.680904388427599</v>
-      </c>
-      <c r="D30" s="16">
-        <f>1.51419639587402*2</f>
-        <v>3.0283927917480402</v>
-      </c>
-      <c r="E30" s="16">
-        <f>1.30200386047363*2</f>
-        <v>2.6040077209472599</v>
-      </c>
-      <c r="F30" s="20">
-        <f>(1.51419639587402+1.30200386047363)*2</f>
-        <v>5.6324005126953001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="B31" s="20">
-        <f>181407.611846923/1000</f>
-        <v>181.407611846923</v>
-      </c>
-      <c r="C31" s="20">
-        <f>17.8208351135253*2</f>
-        <v>35.641670227050597</v>
-      </c>
-      <c r="D31" s="16">
-        <f>2.16889381408691*2</f>
-        <v>4.3377876281738201</v>
-      </c>
-      <c r="E31" s="16">
-        <f>2.19559669494628*2</f>
-        <v>4.3911933898925604</v>
-      </c>
-      <c r="F31" s="20">
-        <f>(2.16889381408691+2.19559669494628)*2</f>
-        <v>8.7289810180663814</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="B32" s="20">
-        <f>361442.13104248/1000</f>
-        <v>361.44213104248001</v>
-      </c>
-      <c r="C32" s="20">
-        <f>35.994529724121*2</f>
-        <v>71.989059448242003</v>
-      </c>
-      <c r="D32" s="16">
-        <f>9.69624519348144*2</f>
-        <v>19.39249038696288</v>
-      </c>
-      <c r="E32" s="16">
-        <f>4.47344779968261*2</f>
-        <v>8.9468955993652202</v>
-      </c>
-      <c r="F32" s="20">
-        <f>(9.69624519348144+4.47344779968261)*2</f>
-        <v>28.3393859863281</v>
-      </c>
-    </row>
+      <c r="E24" s="15"/>
+    </row>
+    <row r="27" spans="1:5" s="5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" s="5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="J10:K10"/>
+  <mergeCells count="7">
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="E20:E24"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="G3:G7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="B18:D18"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="G10:H10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3177A52-BCF1-4EE9-BA1F-11F92B4F0056}">
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="6" width="20.625" customWidth="1"/>
+    <col min="9" max="11" width="24.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="12"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+    </row>
+    <row r="2" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="19"/>
+    </row>
+    <row r="3" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11">
+        <v>6910.71</v>
+      </c>
+      <c r="C3" s="11">
+        <v>3830.97</v>
+      </c>
+      <c r="D3" s="11">
+        <v>3079.48</v>
+      </c>
+      <c r="E3" s="11">
+        <v>0.144703</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="4">
+        <v>4.3087999999999997</v>
+      </c>
+      <c r="J3" s="4">
+        <v>3.2119</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>6</v>
+      </c>
+      <c r="B4" s="11">
+        <v>1372.81</v>
+      </c>
+      <c r="C4" s="11">
+        <v>762.75599999999997</v>
+      </c>
+      <c r="D4" s="11">
+        <v>612.16899999999998</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0.72843100000000005</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>12</v>
+      </c>
+      <c r="B5" s="11">
+        <v>1121.08</v>
+      </c>
+      <c r="C5" s="11">
+        <v>585.30600000000004</v>
+      </c>
+      <c r="D5" s="11">
+        <v>535.53700000000003</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.89199600000000001</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+    </row>
+    <row r="6" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>24</v>
+      </c>
+      <c r="B6" s="11">
+        <v>729.32600000000002</v>
+      </c>
+      <c r="C6" s="11">
+        <v>387.66500000000002</v>
+      </c>
+      <c r="D6" s="11">
+        <v>350.73</v>
+      </c>
+      <c r="E6" s="11">
+        <v>1.37113</v>
+      </c>
+      <c r="F6" s="17"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+    </row>
+    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+    </row>
+    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+    </row>
+    <row r="9" spans="1:12" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+    </row>
+    <row r="10" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L10" s="19"/>
+    </row>
+    <row r="11" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="11">
+        <v>35243.300000000003</v>
+      </c>
+      <c r="C11" s="11">
+        <v>31467.200000000001</v>
+      </c>
+      <c r="D11" s="11">
+        <v>3775.9</v>
+      </c>
+      <c r="E11" s="11">
+        <v>2.8374199999999999E-2</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="4">
+        <v>36.391800000000003</v>
+      </c>
+      <c r="J11" s="4">
+        <v>3.5087999999999999</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="19"/>
+    </row>
+    <row r="12" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>6</v>
+      </c>
+      <c r="B12" s="11">
+        <v>6940.81</v>
+      </c>
+      <c r="C12" s="11">
+        <v>6200.05</v>
+      </c>
+      <c r="D12" s="11">
+        <v>741.91600000000005</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0.14407500000000001</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+    </row>
+    <row r="13" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11">
+        <v>4624.46</v>
+      </c>
+      <c r="C13" s="11">
+        <v>4126.6499999999996</v>
+      </c>
+      <c r="D13" s="11">
+        <v>497.56099999999998</v>
+      </c>
+      <c r="E13" s="11">
+        <v>0.21624199999999999</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>24</v>
+      </c>
+      <c r="B14" s="11">
+        <v>3510.28</v>
+      </c>
+      <c r="C14" s="11">
+        <v>3087.83</v>
+      </c>
+      <c r="D14" s="11">
+        <v>423.64100000000002</v>
+      </c>
+      <c r="E14" s="11">
+        <v>0.28487699999999999</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+    </row>
+    <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+    </row>
+    <row r="17" spans="1:12" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="12"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+    </row>
+    <row r="18" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="19"/>
+    </row>
+    <row r="19" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>1</v>
+      </c>
+      <c r="B19" s="11">
+        <v>674.928</v>
+      </c>
+      <c r="C19" s="11">
+        <v>636.6</v>
+      </c>
+      <c r="D19" s="11">
+        <v>37.942999999999998</v>
+      </c>
+      <c r="E19" s="11">
+        <v>1.4816400000000001</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="4">
+        <v>0.73550000000000004</v>
+      </c>
+      <c r="J19" s="4">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="L19" s="19"/>
+    </row>
+    <row r="20" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>6</v>
+      </c>
+      <c r="B20" s="11">
+        <v>146.78700000000001</v>
+      </c>
+      <c r="C20" s="11">
+        <v>138.12899999999999</v>
+      </c>
+      <c r="D20" s="11">
+        <v>7.9686500000000002</v>
+      </c>
+      <c r="E20" s="11">
+        <v>6.8126100000000003</v>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+    </row>
+    <row r="21" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>12</v>
+      </c>
+      <c r="B21" s="11">
+        <v>113.054</v>
+      </c>
+      <c r="C21" s="11">
+        <v>106.197</v>
+      </c>
+      <c r="D21" s="11">
+        <v>7.3671100000000003</v>
+      </c>
+      <c r="E21" s="11">
+        <v>8.7677499999999995</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+    </row>
+    <row r="22" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>24</v>
+      </c>
+      <c r="B22" s="11">
+        <v>67.190799999999996</v>
+      </c>
+      <c r="C22" s="11">
+        <v>57.0351</v>
+      </c>
+      <c r="D22" s="11">
+        <v>4.1134500000000003</v>
+      </c>
+      <c r="E22" s="11">
+        <v>14.882999999999999</v>
+      </c>
+      <c r="F22" s="17"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+    </row>
+    <row r="24" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+    </row>
+    <row r="25" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+    </row>
+    <row r="26" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+    </row>
+    <row r="27" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+    </row>
+    <row r="28" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+    </row>
+    <row r="29" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+    </row>
+    <row r="30" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+    </row>
+    <row r="32" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I9:J9"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53179F2A-CB60-40DB-A400-8EFEB623165E}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="6" width="24.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:6" ht="169.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11">
+        <f>66672.4801063537/1000</f>
+        <v>66.672480106353703</v>
+      </c>
+      <c r="C3" s="11">
+        <f>1.06430053710937*2</f>
+        <v>2.1286010742187398</v>
+      </c>
+      <c r="D3" s="8">
+        <f>0.271797180175781*2</f>
+        <v>0.54359436035156194</v>
+      </c>
+      <c r="E3" s="8">
+        <f>0.0162124633789062*2</f>
+        <v>3.2424926757812403E-2</v>
+      </c>
+      <c r="F3" s="11">
+        <f>(0.271797180175781+0.0162124633789062)*2</f>
+        <v>0.57601928710937433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="B4" s="11">
+        <f>104542.313814163/1000</f>
+        <v>104.54231381416301</v>
+      </c>
+      <c r="C4" s="11">
+        <f>10.3404521942138*2</f>
+        <v>20.680904388427599</v>
+      </c>
+      <c r="D4" s="8">
+        <f>1.51419639587402*2</f>
+        <v>3.0283927917480402</v>
+      </c>
+      <c r="E4" s="8">
+        <f>1.30200386047363*2</f>
+        <v>2.6040077209472599</v>
+      </c>
+      <c r="F4" s="11">
+        <f>(1.51419639587402+1.30200386047363)*2</f>
+        <v>5.6324005126953001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="B5" s="11">
+        <f>181407.611846923/1000</f>
+        <v>181.407611846923</v>
+      </c>
+      <c r="C5" s="11">
+        <f>17.8208351135253*2</f>
+        <v>35.641670227050597</v>
+      </c>
+      <c r="D5" s="8">
+        <f>2.16889381408691*2</f>
+        <v>4.3377876281738201</v>
+      </c>
+      <c r="E5" s="8">
+        <f>2.19559669494628*2</f>
+        <v>4.3911933898925604</v>
+      </c>
+      <c r="F5" s="11">
+        <f>(2.16889381408691+2.19559669494628)*2</f>
+        <v>8.7289810180663814</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="B6" s="11">
+        <f>361442.13104248/1000</f>
+        <v>361.44213104248001</v>
+      </c>
+      <c r="C6" s="11">
+        <f>35.994529724121*2</f>
+        <v>71.989059448242003</v>
+      </c>
+      <c r="D6" s="8">
+        <f>9.69624519348144*2</f>
+        <v>19.39249038696288</v>
+      </c>
+      <c r="E6" s="8">
+        <f>4.47344779968261*2</f>
+        <v>8.9468955993652202</v>
+      </c>
+      <c r="F6" s="11">
+        <f>(9.69624519348144+4.47344779968261)*2</f>
+        <v>28.3393859863281</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/开销记录/国网数科.xlsx
+++ b/开销记录/国网数科.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aptx4869\Desktop\GWSK-CP-ABE\开销记录\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02CA1AC-CB47-43F2-AF23-EE6434AAFCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE427E9-9E28-48CE-9DC3-BCFAE0CB84C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="CP-ABE" sheetId="1" r:id="rId1"/>
+    <sheet name="签名认证" sheetId="2" r:id="rId2"/>
+    <sheet name="性能表现" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
   <si>
     <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1342,6 +1342,65 @@
   </si>
   <si>
     <r>
+      <t>112</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比特安全</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>RSA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">密钥对
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>版本
+2^8</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -1392,21 +1451,16 @@
       </rPr>
       <t>比特安全</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>112</t>
-    </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>比特安全</t>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2^10</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1419,7 +1473,7 @@
     <numFmt numFmtId="176" formatCode="0.0000"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1610,6 +1664,12 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1655,7 +1715,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1723,19 +1783,78 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1752,9 +1871,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1764,26 +1880,69 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1791,14 +1950,10 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2090,17 +2245,17 @@
     <col min="18" max="16384" width="8.875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:7" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:7" s="5" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+    </row>
+    <row r="2" spans="1:7" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2123,134 +2278,134 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>10</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="15">
         <v>2.5573350000000001</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="12">
         <v>42.859974999999999</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="12">
         <v>43.620930999999999</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="12">
         <v>11.885471000000001</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="12">
         <v>6.7905999999999994E-2</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>20</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="16">
         <v>2.6740780000000002</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="13">
         <v>76.995339999999999</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="13">
         <v>85.151117999999997</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="13">
         <v>22.811855000000001</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="13">
         <v>6.9924E-2</v>
       </c>
-      <c r="G4" s="14"/>
-    </row>
-    <row r="5" spans="1:7" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>30</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="16">
         <v>2.8359990000000002</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="13">
         <v>106.997899</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="13">
         <v>123.02942299999999</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="13">
         <v>32.390200999999998</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="13">
         <v>6.5294000000000005E-2</v>
       </c>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:7" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="26"/>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>40</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="16">
         <v>2.6853229999999999</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="13">
         <v>138.55750699999999</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="13">
         <v>161.911518</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="13">
         <v>45.437337999999997</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="13">
         <v>6.5157999999999994E-2</v>
       </c>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:7" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>50</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="17">
         <v>2.7396410000000002</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="14">
         <v>171.35196300000001</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="14">
         <v>202.050907</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="14">
         <v>53.874381999999997</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="14">
         <v>6.6238000000000005E-2</v>
       </c>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="22" t="s">
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-    </row>
-    <row r="10" spans="1:7" s="5" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+    </row>
+    <row r="10" spans="1:7" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:7" s="5" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -2267,190 +2422,194 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="5" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="19">
         <v>66.0244</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="22">
         <v>2.7</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="22">
         <v>0.9</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="28" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="20">
         <v>131.98480000000001</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="23">
         <v>2.8</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="23">
         <v>0.9</v>
       </c>
-      <c r="E13" s="15"/>
-    </row>
-    <row r="14" spans="1:7" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="28"/>
+    </row>
+    <row r="14" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="20">
         <v>277.15370000000001</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="23">
         <v>2.9</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="23">
         <v>0.9</v>
       </c>
-      <c r="E14" s="15"/>
-    </row>
-    <row r="15" spans="1:7" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="28"/>
+    </row>
+    <row r="15" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="20">
         <v>525.71910000000003</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="23">
         <v>2.9</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="23">
         <v>0.9</v>
       </c>
-      <c r="E15" s="15"/>
-    </row>
-    <row r="16" spans="1:7" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="28"/>
+    </row>
+    <row r="16" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="21">
         <v>1055.6633999999999</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="24">
         <v>2.9</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="24">
         <v>0.9</v>
       </c>
-      <c r="E16" s="15"/>
-    </row>
-    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="5" t="s">
+      <c r="E16" s="28"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="18" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="16" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-    </row>
-    <row r="19" spans="1:5" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:5" s="5" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+    </row>
+    <row r="20" spans="1:5" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="19">
         <v>66.740399999999994</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="19">
         <v>1.3420000000000001</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="19">
         <v>0.59289999999999998</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="28" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="20">
         <v>133.6474</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="20">
         <v>1.2630999999999999</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="20">
         <v>0.56310000000000004</v>
       </c>
-      <c r="E21" s="15"/>
-    </row>
-    <row r="22" spans="1:5" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="28"/>
+    </row>
+    <row r="22" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="20">
         <v>265.58280000000002</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="20">
         <v>1.3405</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="20">
         <v>0.59030000000000005</v>
       </c>
-      <c r="E22" s="15"/>
-    </row>
-    <row r="23" spans="1:5" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E22" s="28"/>
+    </row>
+    <row r="23" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="20">
         <v>532.73979999999995</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="20">
         <v>1.2676000000000001</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="20">
         <v>0.56110000000000004</v>
       </c>
-      <c r="E23" s="15"/>
-    </row>
-    <row r="24" spans="1:5" s="5" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="28"/>
+    </row>
+    <row r="24" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="21">
         <v>1063.7551000000001</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="21">
         <v>1.3016000000000001</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="21">
         <v>0.59379999999999999</v>
       </c>
-      <c r="E24" s="15"/>
-    </row>
-    <row r="27" spans="1:5" s="5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" s="5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="E24" s="28"/>
+    </row>
+    <row r="27" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="E20:E24"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="G3:G7"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2468,22 +2627,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="12" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
     </row>
     <row r="2" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2504,8 +2663,8 @@
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
       <c r="I2" s="1" t="s">
         <v>25</v>
       </c>
@@ -2515,157 +2674,157 @@
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="19"/>
+      <c r="L2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="9">
         <v>6910.71</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="9">
         <v>3830.97</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="9">
         <v>3079.48</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="9">
         <v>0.144703</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
       <c r="I3" s="4">
         <v>4.3087999999999997</v>
       </c>
       <c r="J3" s="4">
         <v>3.2119</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="19"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>6</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="9">
         <v>1372.81</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="9">
         <v>762.75599999999997</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="9">
         <v>612.16899999999998</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <v>0.72843100000000005</v>
       </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>12</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="9">
         <v>1121.08</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <v>585.30600000000004</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="9">
         <v>535.53700000000003</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <v>0.89199600000000001</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>24</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <v>729.32600000000002</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <v>387.66500000000002</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <v>350.73</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <v>1.37113</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:12" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="12" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
     </row>
     <row r="10" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -2686,8 +2845,8 @@
       <c r="F10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="1" t="s">
         <v>25</v>
       </c>
@@ -2697,157 +2856,157 @@
       <c r="K10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L10" s="19"/>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>1</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <v>35243.300000000003</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <v>31467.200000000001</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <v>3775.9</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <v>2.8374199999999999E-2</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
       <c r="I11" s="4">
         <v>36.391800000000003</v>
       </c>
       <c r="J11" s="4">
         <v>3.5087999999999999</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="19"/>
+      <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>6</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <v>6940.81</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="9">
         <v>6200.05</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="9">
         <v>741.91600000000005</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <v>0.14407500000000001</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="9">
         <v>4624.46</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="9">
         <v>4126.6499999999996</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="9">
         <v>497.56099999999998</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <v>0.21624199999999999</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
     </row>
     <row r="14" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="9">
         <v>3510.28</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="9">
         <v>3087.83</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="9">
         <v>423.64100000000002</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <v>0.28487699999999999</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
     </row>
     <row r="15" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
     </row>
     <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
     </row>
     <row r="17" spans="1:12" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="12" t="s">
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
     </row>
     <row r="18" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -2868,8 +3027,8 @@
       <c r="F18" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
       <c r="I18" s="1" t="s">
         <v>25</v>
       </c>
@@ -2879,292 +3038,292 @@
       <c r="K18" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L18" s="19"/>
+      <c r="L18" s="10"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>1</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="9">
         <v>674.928</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="9">
         <v>636.6</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="9">
         <v>37.942999999999998</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="9">
         <v>1.4816400000000001</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="F19" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
       <c r="I19" s="4">
         <v>0.73550000000000004</v>
       </c>
       <c r="J19" s="4">
         <v>3.8300000000000001E-2</v>
       </c>
-      <c r="K19" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="L19" s="19"/>
+      <c r="K19" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19" s="10"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>6</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>146.78700000000001</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="9">
         <v>138.12899999999999</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="9">
         <v>7.9686500000000002</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="9">
         <v>6.8126100000000003</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>12</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>113.054</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="9">
         <v>106.197</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="9">
         <v>7.3671100000000003</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="9">
         <v>8.7677499999999995</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>24</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <v>67.190799999999996</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="9">
         <v>57.0351</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="9">
         <v>4.1134500000000003</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="9">
         <v>14.882999999999999</v>
       </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
     </row>
     <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
     </row>
     <row r="24" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
     </row>
     <row r="25" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
     </row>
     <row r="26" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
     </row>
     <row r="27" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
     </row>
     <row r="28" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
     </row>
     <row r="29" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
     </row>
     <row r="30" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
     </row>
     <row r="31" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
     </row>
     <row r="32" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
     </row>
     <row r="33" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
     </row>
     <row r="34" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
     </row>
     <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3180,29 +3339,32 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53179F2A-CB60-40DB-A400-8EFEB623165E}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="24.625" customWidth="1"/>
+    <col min="7" max="7" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:7" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:6" ht="169.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+    </row>
+    <row r="2" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -3220,112 +3382,123 @@
       <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="9">
         <f>66672.4801063537/1000</f>
         <v>66.672480106353703</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="9">
         <f>1.06430053710937*2</f>
         <v>2.1286010742187398</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <f>0.271797180175781*2</f>
         <v>0.54359436035156194</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <f>0.0162124633789062*2</f>
         <v>3.2424926757812403E-2</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="9">
         <f>(0.271797180175781+0.0162124633789062)*2</f>
         <v>0.57601928710937433</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>0.7</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="9">
         <f>104542.313814163/1000</f>
         <v>104.54231381416301</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="9">
         <f>10.3404521942138*2</f>
         <v>20.680904388427599</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <f>1.51419639587402*2</f>
         <v>3.0283927917480402</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <f>1.30200386047363*2</f>
         <v>2.6040077209472599</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <f>(1.51419639587402+1.30200386047363)*2</f>
         <v>5.6324005126953001</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="34"/>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>0.4</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="9">
         <f>181407.611846923/1000</f>
         <v>181.407611846923</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <f>17.8208351135253*2</f>
         <v>35.641670227050597</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <f>2.16889381408691*2</f>
         <v>4.3377876281738201</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <f>2.19559669494628*2</f>
         <v>4.3911933898925604</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="9">
         <f>(2.16889381408691+2.19559669494628)*2</f>
         <v>8.7289810180663814</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="34"/>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>0.2</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <f>361442.13104248/1000</f>
         <v>361.44213104248001</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <f>35.994529724121*2</f>
         <v>71.989059448242003</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f>9.69624519348144*2</f>
         <v>19.39249038696288</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f>4.47344779968261*2</f>
         <v>8.9468955993652202</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <f>(9.69624519348144+4.47344779968261)*2</f>
         <v>28.3393859863281</v>
       </c>
+      <c r="G6" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="G3:G6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>